--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753523</v>
+        <v>127753529</v>
       </c>
       <c r="B7" t="n">
-        <v>92626</v>
+        <v>92815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743213</v>
+        <v>743161</v>
       </c>
       <c r="R7" t="n">
-        <v>7152697</v>
+        <v>7152726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753529</v>
+        <v>127753523</v>
       </c>
       <c r="B8" t="n">
-        <v>92815</v>
+        <v>92626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743161</v>
+        <v>743213</v>
       </c>
       <c r="R8" t="n">
-        <v>7152726</v>
+        <v>7152697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753543</v>
+        <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>92622</v>
+        <v>92815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743147</v>
+        <v>743184</v>
       </c>
       <c r="R9" t="n">
-        <v>7152782</v>
+        <v>7152932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753526</v>
+        <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92815</v>
+        <v>92622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743184</v>
+        <v>743147</v>
       </c>
       <c r="R11" t="n">
-        <v>7152932</v>
+        <v>7152782</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753540</v>
+        <v>127753547</v>
       </c>
       <c r="B16" t="n">
-        <v>78687</v>
+        <v>92622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743256</v>
+        <v>743197</v>
       </c>
       <c r="R16" t="n">
-        <v>7152743</v>
+        <v>7152675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753547</v>
+        <v>127753540</v>
       </c>
       <c r="B17" t="n">
-        <v>92622</v>
+        <v>78687</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>743197</v>
+        <v>743256</v>
       </c>
       <c r="R17" t="n">
-        <v>7152675</v>
+        <v>7152743</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753518</v>
+        <v>127753537</v>
       </c>
       <c r="B25" t="n">
-        <v>90367</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743133</v>
+        <v>743060</v>
       </c>
       <c r="R25" t="n">
-        <v>7152823</v>
+        <v>7152820</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753537</v>
+        <v>127753518</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>90367</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3027,21 +3027,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743060</v>
+        <v>743133</v>
       </c>
       <c r="R26" t="n">
-        <v>7152820</v>
+        <v>7152823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3210,10 +3210,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753521</v>
+        <v>127753517</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>90367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3221,42 +3221,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743184</v>
+        <v>743167</v>
       </c>
       <c r="R28" t="n">
-        <v>7152932</v>
+        <v>7152964</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,10 +3307,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753517</v>
+        <v>127753521</v>
       </c>
       <c r="B29" t="n">
-        <v>90367</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,34 +3318,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>743167</v>
+        <v>743184</v>
       </c>
       <c r="R29" t="n">
-        <v>7152964</v>
+        <v>7152932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91346</v>
+        <v>91352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91316</v>
+        <v>91322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753529</v>
+        <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92815</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743161</v>
+        <v>743213</v>
       </c>
       <c r="R7" t="n">
-        <v>7152726</v>
+        <v>7152697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753523</v>
+        <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>92626</v>
+        <v>92821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743213</v>
+        <v>743161</v>
       </c>
       <c r="R8" t="n">
-        <v>7152697</v>
+        <v>7152726</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753526</v>
+        <v>127753527</v>
       </c>
       <c r="B9" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743184</v>
+        <v>743212</v>
       </c>
       <c r="R9" t="n">
-        <v>7152932</v>
+        <v>7152903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753527</v>
+        <v>127753526</v>
       </c>
       <c r="B10" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743212</v>
+        <v>743184</v>
       </c>
       <c r="R10" t="n">
-        <v>7152903</v>
+        <v>7152932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91493</v>
+        <v>91499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753547</v>
+        <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>92622</v>
+        <v>78687</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743197</v>
+        <v>743256</v>
       </c>
       <c r="R16" t="n">
-        <v>7152675</v>
+        <v>7152743</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753540</v>
+        <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>78687</v>
+        <v>92628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>743256</v>
+        <v>743197</v>
       </c>
       <c r="R17" t="n">
-        <v>7152743</v>
+        <v>7152675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92626</v>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753530</v>
+        <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>92060</v>
+        <v>80152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1105</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>743176</v>
+        <v>743242</v>
       </c>
       <c r="R22" t="n">
-        <v>7152744</v>
+        <v>7152788</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,32 +2725,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753522</v>
+        <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>80152</v>
+        <v>92066</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>1105</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>743242</v>
+        <v>743176</v>
       </c>
       <c r="R23" t="n">
-        <v>7152788</v>
+        <v>7152744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>127753518</v>
       </c>
       <c r="B26" t="n">
-        <v>90367</v>
+        <v>90373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127753534</v>
+        <v>127753521</v>
       </c>
       <c r="B27" t="n">
-        <v>91346</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3124,34 +3124,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>743129</v>
+        <v>743184</v>
       </c>
       <c r="R27" t="n">
-        <v>7152731</v>
+        <v>7152932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3210,10 +3218,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753517</v>
+        <v>127753534</v>
       </c>
       <c r="B28" t="n">
-        <v>90367</v>
+        <v>91352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3221,21 +3229,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3245,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743167</v>
+        <v>743129</v>
       </c>
       <c r="R28" t="n">
-        <v>7152964</v>
+        <v>7152731</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3307,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753521</v>
+        <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>90373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3318,42 +3326,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>743184</v>
+        <v>743167</v>
       </c>
       <c r="R29" t="n">
-        <v>7152932</v>
+        <v>7152964</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91593</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>77998</v>
+        <v>78001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91322</v>
+        <v>91325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753523</v>
+        <v>127753529</v>
       </c>
       <c r="B7" t="n">
-        <v>92632</v>
+        <v>92824</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743213</v>
+        <v>743161</v>
       </c>
       <c r="R7" t="n">
-        <v>7152697</v>
+        <v>7152726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753529</v>
+        <v>127753523</v>
       </c>
       <c r="B8" t="n">
-        <v>92821</v>
+        <v>92635</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743161</v>
+        <v>743213</v>
       </c>
       <c r="R8" t="n">
-        <v>7152726</v>
+        <v>7152697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753527</v>
+        <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743212</v>
+        <v>743184</v>
       </c>
       <c r="R9" t="n">
-        <v>7152903</v>
+        <v>7152932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753526</v>
+        <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743184</v>
+        <v>743212</v>
       </c>
       <c r="R10" t="n">
-        <v>7152932</v>
+        <v>7152903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127753520</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753540</v>
+        <v>127753547</v>
       </c>
       <c r="B16" t="n">
-        <v>78687</v>
+        <v>92631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743256</v>
+        <v>743197</v>
       </c>
       <c r="R16" t="n">
-        <v>7152743</v>
+        <v>7152675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753547</v>
+        <v>127753540</v>
       </c>
       <c r="B17" t="n">
-        <v>92628</v>
+        <v>78690</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>743197</v>
+        <v>743256</v>
       </c>
       <c r="R17" t="n">
-        <v>7152675</v>
+        <v>7152743</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92632</v>
+        <v>92635</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92066</v>
+        <v>92069</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753537</v>
+        <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>90376</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743060</v>
+        <v>743133</v>
       </c>
       <c r="R25" t="n">
-        <v>7152820</v>
+        <v>7152823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753518</v>
+        <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>90373</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3027,21 +3027,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743133</v>
+        <v>743060</v>
       </c>
       <c r="R26" t="n">
-        <v>7152823</v>
+        <v>7152820</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127753521</v>
+        <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>91355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3124,42 +3124,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>743184</v>
+        <v>743129</v>
       </c>
       <c r="R27" t="n">
-        <v>7152932</v>
+        <v>7152731</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3218,10 +3210,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753534</v>
+        <v>127753517</v>
       </c>
       <c r="B28" t="n">
-        <v>91352</v>
+        <v>90376</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3229,21 +3221,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3245,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743129</v>
+        <v>743167</v>
       </c>
       <c r="R28" t="n">
-        <v>7152731</v>
+        <v>7152964</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,10 +3307,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753517</v>
+        <v>127753521</v>
       </c>
       <c r="B29" t="n">
-        <v>90373</v>
+        <v>57826</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,34 +3318,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>743167</v>
+        <v>743184</v>
       </c>
       <c r="R29" t="n">
-        <v>7152964</v>
+        <v>7152932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753528</v>
+        <v>127753544</v>
       </c>
       <c r="B3" t="n">
-        <v>92824</v>
+        <v>92639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743133</v>
+        <v>743130</v>
       </c>
       <c r="R3" t="n">
-        <v>7152823</v>
+        <v>7152722</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753544</v>
+        <v>127753528</v>
       </c>
       <c r="B4" t="n">
-        <v>92631</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743130</v>
+        <v>743133</v>
       </c>
       <c r="R4" t="n">
-        <v>7152722</v>
+        <v>7152823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127753548</v>
+        <v>127753525</v>
       </c>
       <c r="B5" t="n">
-        <v>78001</v>
+        <v>91333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743086</v>
+        <v>743160</v>
       </c>
       <c r="R5" t="n">
-        <v>7152983</v>
+        <v>7152830</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753525</v>
+        <v>127753548</v>
       </c>
       <c r="B6" t="n">
-        <v>91325</v>
+        <v>78007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>743160</v>
+        <v>743086</v>
       </c>
       <c r="R6" t="n">
-        <v>7152830</v>
+        <v>7152983</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753529</v>
+        <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92824</v>
+        <v>92643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743161</v>
+        <v>743213</v>
       </c>
       <c r="R7" t="n">
-        <v>7152726</v>
+        <v>7152697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753523</v>
+        <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>92635</v>
+        <v>92832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743213</v>
+        <v>743161</v>
       </c>
       <c r="R8" t="n">
-        <v>7152697</v>
+        <v>7152726</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753526</v>
+        <v>127753527</v>
       </c>
       <c r="B9" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743184</v>
+        <v>743212</v>
       </c>
       <c r="R9" t="n">
-        <v>7152932</v>
+        <v>7152903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753527</v>
+        <v>127753526</v>
       </c>
       <c r="B10" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743212</v>
+        <v>743184</v>
       </c>
       <c r="R10" t="n">
-        <v>7152903</v>
+        <v>7152932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127753520</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91502</v>
+        <v>91510</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753547</v>
+        <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>92631</v>
+        <v>78696</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743197</v>
+        <v>743256</v>
       </c>
       <c r="R16" t="n">
-        <v>7152675</v>
+        <v>7152743</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753540</v>
+        <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>78690</v>
+        <v>92639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>743256</v>
+        <v>743197</v>
       </c>
       <c r="R17" t="n">
-        <v>7152743</v>
+        <v>7152675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92635</v>
+        <v>92643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753522</v>
+        <v>127753530</v>
       </c>
       <c r="B22" t="n">
-        <v>80155</v>
+        <v>92077</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>1105</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>743242</v>
+        <v>743176</v>
       </c>
       <c r="R22" t="n">
-        <v>7152788</v>
+        <v>7152744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,32 +2725,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753530</v>
+        <v>127753522</v>
       </c>
       <c r="B23" t="n">
-        <v>92069</v>
+        <v>80161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1105</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>743176</v>
+        <v>743242</v>
       </c>
       <c r="R23" t="n">
-        <v>7152744</v>
+        <v>7152788</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90376</v>
+        <v>90384</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>127753517</v>
       </c>
       <c r="B28" t="n">
-        <v>90376</v>
+        <v>90384</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>127753521</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91602</v>
+        <v>91610</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753544</v>
+        <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92639</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743130</v>
+        <v>743133</v>
       </c>
       <c r="R3" t="n">
-        <v>7152722</v>
+        <v>7152823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753528</v>
+        <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>92640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743133</v>
+        <v>743130</v>
       </c>
       <c r="R4" t="n">
-        <v>7152823</v>
+        <v>7152722</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127753525</v>
+        <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>91333</v>
+        <v>78007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743160</v>
+        <v>743086</v>
       </c>
       <c r="R5" t="n">
-        <v>7152830</v>
+        <v>7152983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753548</v>
+        <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>78007</v>
+        <v>91334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>743086</v>
+        <v>743160</v>
       </c>
       <c r="R6" t="n">
-        <v>7152983</v>
+        <v>7152830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753523</v>
+        <v>127753529</v>
       </c>
       <c r="B7" t="n">
-        <v>92643</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743213</v>
+        <v>743161</v>
       </c>
       <c r="R7" t="n">
-        <v>7152697</v>
+        <v>7152726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753529</v>
+        <v>127753523</v>
       </c>
       <c r="B8" t="n">
-        <v>92832</v>
+        <v>92644</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743161</v>
+        <v>743213</v>
       </c>
       <c r="R8" t="n">
-        <v>7152726</v>
+        <v>7152697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>127753527</v>
       </c>
       <c r="B9" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127753526</v>
       </c>
       <c r="B10" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91510</v>
+        <v>91511</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92643</v>
+        <v>92644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>127753530</v>
       </c>
       <c r="B22" t="n">
-        <v>92077</v>
+        <v>92078</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90384</v>
+        <v>90385</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>127753517</v>
       </c>
       <c r="B28" t="n">
-        <v>90384</v>
+        <v>90385</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91610</v>
+        <v>91611</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753528</v>
+        <v>127753544</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>92640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743133</v>
+        <v>743130</v>
       </c>
       <c r="R3" t="n">
-        <v>7152823</v>
+        <v>7152722</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753544</v>
+        <v>127753528</v>
       </c>
       <c r="B4" t="n">
-        <v>92640</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743130</v>
+        <v>743133</v>
       </c>
       <c r="R4" t="n">
-        <v>7152722</v>
+        <v>7152823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127753548</v>
+        <v>127753525</v>
       </c>
       <c r="B5" t="n">
-        <v>78007</v>
+        <v>91334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743086</v>
+        <v>743160</v>
       </c>
       <c r="R5" t="n">
-        <v>7152983</v>
+        <v>7152830</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753525</v>
+        <v>127753548</v>
       </c>
       <c r="B6" t="n">
-        <v>91334</v>
+        <v>78007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>743160</v>
+        <v>743086</v>
       </c>
       <c r="R6" t="n">
-        <v>7152830</v>
+        <v>7152983</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753527</v>
+        <v>127753543</v>
       </c>
       <c r="B9" t="n">
-        <v>92833</v>
+        <v>92640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743212</v>
+        <v>743147</v>
       </c>
       <c r="R9" t="n">
-        <v>7152903</v>
+        <v>7152782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753526</v>
+        <v>127753527</v>
       </c>
       <c r="B10" t="n">
         <v>92833</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743184</v>
+        <v>743212</v>
       </c>
       <c r="R10" t="n">
-        <v>7152932</v>
+        <v>7152903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753543</v>
+        <v>127753526</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>92833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743147</v>
+        <v>743184</v>
       </c>
       <c r="R11" t="n">
-        <v>7152782</v>
+        <v>7152932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2240,7 +2240,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127753542</v>
+        <v>127753541</v>
       </c>
       <c r="B18" t="n">
         <v>92640</v>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>743197</v>
+        <v>743108</v>
       </c>
       <c r="R18" t="n">
-        <v>7152921</v>
+        <v>7152950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753541</v>
+        <v>127753542</v>
       </c>
       <c r="B19" t="n">
         <v>92640</v>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>743108</v>
+        <v>743197</v>
       </c>
       <c r="R19" t="n">
-        <v>7152950</v>
+        <v>7152921</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753518</v>
+        <v>127753537</v>
       </c>
       <c r="B25" t="n">
-        <v>90385</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743133</v>
+        <v>743060</v>
       </c>
       <c r="R25" t="n">
-        <v>7152823</v>
+        <v>7152820</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753537</v>
+        <v>127753518</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>90385</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3027,21 +3027,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743060</v>
+        <v>743133</v>
       </c>
       <c r="R26" t="n">
-        <v>7152820</v>
+        <v>7152823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753544</v>
+        <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92640</v>
+        <v>92834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743130</v>
+        <v>743133</v>
       </c>
       <c r="R3" t="n">
-        <v>7152722</v>
+        <v>7152823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753528</v>
+        <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743133</v>
+        <v>743130</v>
       </c>
       <c r="R4" t="n">
-        <v>7152823</v>
+        <v>7152722</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127753525</v>
       </c>
       <c r="B5" t="n">
-        <v>91334</v>
+        <v>91335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127753529</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127753523</v>
       </c>
       <c r="B8" t="n">
-        <v>92644</v>
+        <v>92645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753543</v>
+        <v>127753527</v>
       </c>
       <c r="B9" t="n">
-        <v>92640</v>
+        <v>92834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743147</v>
+        <v>743212</v>
       </c>
       <c r="R9" t="n">
-        <v>7152782</v>
+        <v>7152903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753527</v>
+        <v>127753543</v>
       </c>
       <c r="B10" t="n">
-        <v>92833</v>
+        <v>92641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743212</v>
+        <v>743147</v>
       </c>
       <c r="R10" t="n">
-        <v>7152903</v>
+        <v>7152782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>127753526</v>
       </c>
       <c r="B11" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91511</v>
+        <v>91512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753540</v>
+        <v>127753547</v>
       </c>
       <c r="B16" t="n">
-        <v>78696</v>
+        <v>92641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743256</v>
+        <v>743197</v>
       </c>
       <c r="R16" t="n">
-        <v>7152743</v>
+        <v>7152675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753547</v>
+        <v>127753540</v>
       </c>
       <c r="B17" t="n">
-        <v>92640</v>
+        <v>78696</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>743197</v>
+        <v>743256</v>
       </c>
       <c r="R17" t="n">
-        <v>7152675</v>
+        <v>7152743</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127753541</v>
+        <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>743108</v>
+        <v>743197</v>
       </c>
       <c r="R18" t="n">
-        <v>7152950</v>
+        <v>7152921</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753542</v>
+        <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>743197</v>
+        <v>743108</v>
       </c>
       <c r="R19" t="n">
-        <v>7152921</v>
+        <v>7152950</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92644</v>
+        <v>92645</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>127753530</v>
       </c>
       <c r="B22" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753537</v>
+        <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>90386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743060</v>
+        <v>743133</v>
       </c>
       <c r="R25" t="n">
-        <v>7152820</v>
+        <v>7152823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753518</v>
+        <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>90385</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3027,21 +3027,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743133</v>
+        <v>743060</v>
       </c>
       <c r="R26" t="n">
-        <v>7152823</v>
+        <v>7152820</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3116,7 +3116,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753517</v>
+        <v>127753521</v>
       </c>
       <c r="B28" t="n">
-        <v>90385</v>
+        <v>57832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3221,34 +3221,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743167</v>
+        <v>743184</v>
       </c>
       <c r="R28" t="n">
-        <v>7152964</v>
+        <v>7152932</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3307,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753521</v>
+        <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>57832</v>
+        <v>90386</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3318,42 +3326,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>743184</v>
+        <v>743167</v>
       </c>
       <c r="R29" t="n">
-        <v>7152932</v>
+        <v>7152964</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91611</v>
+        <v>91612</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127753525</v>
       </c>
       <c r="B5" t="n">
-        <v>91335</v>
+        <v>91336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127753529</v>
       </c>
       <c r="B7" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127753523</v>
       </c>
       <c r="B8" t="n">
-        <v>92645</v>
+        <v>92646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127753527</v>
       </c>
       <c r="B9" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753543</v>
+        <v>127753526</v>
       </c>
       <c r="B10" t="n">
-        <v>92641</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743147</v>
+        <v>743184</v>
       </c>
       <c r="R10" t="n">
-        <v>7152782</v>
+        <v>7152932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753526</v>
+        <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92834</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743184</v>
+        <v>743147</v>
       </c>
       <c r="R11" t="n">
-        <v>7152932</v>
+        <v>7152782</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753547</v>
+        <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>92641</v>
+        <v>78696</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743197</v>
+        <v>743256</v>
       </c>
       <c r="R16" t="n">
-        <v>7152675</v>
+        <v>7152743</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753540</v>
+        <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>78696</v>
+        <v>92642</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>743256</v>
+        <v>743197</v>
       </c>
       <c r="R17" t="n">
-        <v>7152743</v>
+        <v>7152675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92645</v>
+        <v>92646</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>127753530</v>
       </c>
       <c r="B22" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90386</v>
+        <v>90387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753521</v>
+        <v>127753517</v>
       </c>
       <c r="B28" t="n">
-        <v>57832</v>
+        <v>90387</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3221,42 +3221,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743184</v>
+        <v>743167</v>
       </c>
       <c r="R28" t="n">
-        <v>7152932</v>
+        <v>7152964</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,10 +3307,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753517</v>
+        <v>127753521</v>
       </c>
       <c r="B29" t="n">
-        <v>90386</v>
+        <v>57832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,34 +3318,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>743167</v>
+        <v>743184</v>
       </c>
       <c r="R29" t="n">
-        <v>7152964</v>
+        <v>7152932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91612</v>
+        <v>91613</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753527</v>
+        <v>127753543</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743212</v>
+        <v>743147</v>
       </c>
       <c r="R9" t="n">
-        <v>7152903</v>
+        <v>7152782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753543</v>
+        <v>127753527</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743147</v>
+        <v>743212</v>
       </c>
       <c r="R11" t="n">
-        <v>7152782</v>
+        <v>7152903</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753529</v>
+        <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743161</v>
+        <v>743213</v>
       </c>
       <c r="R7" t="n">
-        <v>7152726</v>
+        <v>7152697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753523</v>
+        <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>92646</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743213</v>
+        <v>743161</v>
       </c>
       <c r="R8" t="n">
-        <v>7152697</v>
+        <v>7152726</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753523</v>
+        <v>127753529</v>
       </c>
       <c r="B7" t="n">
-        <v>92646</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743213</v>
+        <v>743161</v>
       </c>
       <c r="R7" t="n">
-        <v>7152697</v>
+        <v>7152726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753529</v>
+        <v>127753523</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743161</v>
+        <v>743213</v>
       </c>
       <c r="R8" t="n">
-        <v>7152726</v>
+        <v>7152697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753530</v>
+        <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>92080</v>
+        <v>80161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1105</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>743176</v>
+        <v>743242</v>
       </c>
       <c r="R22" t="n">
-        <v>7152744</v>
+        <v>7152788</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,32 +2725,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753522</v>
+        <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>80161</v>
+        <v>92080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>1105</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>743242</v>
+        <v>743176</v>
       </c>
       <c r="R23" t="n">
-        <v>7152788</v>
+        <v>7152744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753518</v>
+        <v>127753537</v>
       </c>
       <c r="B25" t="n">
-        <v>90387</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743133</v>
+        <v>743060</v>
       </c>
       <c r="R25" t="n">
-        <v>7152823</v>
+        <v>7152820</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753537</v>
+        <v>127753518</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>90387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3027,21 +3027,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743060</v>
+        <v>743133</v>
       </c>
       <c r="R26" t="n">
-        <v>7152820</v>
+        <v>7152823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753528</v>
+        <v>127753544</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743133</v>
+        <v>743130</v>
       </c>
       <c r="R3" t="n">
-        <v>7152823</v>
+        <v>7152722</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753544</v>
+        <v>127753528</v>
       </c>
       <c r="B4" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743130</v>
+        <v>743133</v>
       </c>
       <c r="R4" t="n">
-        <v>7152722</v>
+        <v>7152823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753537</v>
+        <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>90387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743060</v>
+        <v>743133</v>
       </c>
       <c r="R25" t="n">
-        <v>7152820</v>
+        <v>7152823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753518</v>
+        <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>90387</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3027,21 +3027,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743133</v>
+        <v>743060</v>
       </c>
       <c r="R26" t="n">
-        <v>7152823</v>
+        <v>7152820</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753544</v>
+        <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743130</v>
+        <v>743133</v>
       </c>
       <c r="R3" t="n">
-        <v>7152722</v>
+        <v>7152823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753528</v>
+        <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743133</v>
+        <v>743130</v>
       </c>
       <c r="R4" t="n">
-        <v>7152823</v>
+        <v>7152722</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753523</v>
+        <v>127753529</v>
       </c>
       <c r="B7" t="n">
-        <v>92646</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743213</v>
+        <v>743161</v>
       </c>
       <c r="R7" t="n">
-        <v>7152697</v>
+        <v>7152726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753529</v>
+        <v>127753523</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743161</v>
+        <v>743213</v>
       </c>
       <c r="R8" t="n">
-        <v>7152726</v>
+        <v>7152697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753518</v>
+        <v>127753537</v>
       </c>
       <c r="B25" t="n">
-        <v>90387</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743133</v>
+        <v>743060</v>
       </c>
       <c r="R25" t="n">
-        <v>7152823</v>
+        <v>7152820</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753537</v>
+        <v>127753518</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>90387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3027,21 +3027,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743060</v>
+        <v>743133</v>
       </c>
       <c r="R26" t="n">
-        <v>7152820</v>
+        <v>7152823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -2919,10 +2919,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753537</v>
+        <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>90387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743060</v>
+        <v>743133</v>
       </c>
       <c r="R25" t="n">
-        <v>7152820</v>
+        <v>7152823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753518</v>
+        <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>90387</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3027,21 +3027,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743133</v>
+        <v>743060</v>
       </c>
       <c r="R26" t="n">
-        <v>7152823</v>
+        <v>7152820</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91366</v>
+        <v>91374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127753525</v>
       </c>
       <c r="B5" t="n">
-        <v>91336</v>
+        <v>91344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127753548</v>
       </c>
       <c r="B6" t="n">
-        <v>78007</v>
+        <v>78010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127753529</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127753523</v>
       </c>
       <c r="B8" t="n">
-        <v>92646</v>
+        <v>92654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127753543</v>
       </c>
       <c r="B9" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127753526</v>
       </c>
       <c r="B10" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127753527</v>
       </c>
       <c r="B11" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127753520</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91513</v>
+        <v>91521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92646</v>
+        <v>92654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753522</v>
+        <v>127753530</v>
       </c>
       <c r="B22" t="n">
-        <v>80161</v>
+        <v>92088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>1105</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>743242</v>
+        <v>743176</v>
       </c>
       <c r="R22" t="n">
-        <v>7152788</v>
+        <v>7152744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,32 +2725,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753530</v>
+        <v>127753522</v>
       </c>
       <c r="B23" t="n">
-        <v>92080</v>
+        <v>80164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1105</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>743176</v>
+        <v>743242</v>
       </c>
       <c r="R23" t="n">
-        <v>7152744</v>
+        <v>7152788</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90387</v>
+        <v>90393</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91366</v>
+        <v>91374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>127753517</v>
       </c>
       <c r="B28" t="n">
-        <v>90387</v>
+        <v>90393</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>127753521</v>
       </c>
       <c r="B29" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91613</v>
+        <v>91621</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -3113,10 +3113,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127753534</v>
+        <v>127753521</v>
       </c>
       <c r="B27" t="n">
-        <v>91374</v>
+        <v>57833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3124,34 +3124,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>743129</v>
+        <v>743184</v>
       </c>
       <c r="R27" t="n">
-        <v>7152731</v>
+        <v>7152932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3210,10 +3218,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753517</v>
+        <v>127753534</v>
       </c>
       <c r="B28" t="n">
-        <v>90393</v>
+        <v>91374</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3221,21 +3229,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3245,10 +3253,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743167</v>
+        <v>743129</v>
       </c>
       <c r="R28" t="n">
-        <v>7152964</v>
+        <v>7152731</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3307,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753521</v>
+        <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>57833</v>
+        <v>90393</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3318,42 +3326,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>743184</v>
+        <v>743167</v>
       </c>
       <c r="R29" t="n">
-        <v>7152932</v>
+        <v>7152964</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91374</v>
+        <v>91466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127753525</v>
+        <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>91344</v>
+        <v>78055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743160</v>
+        <v>743086</v>
       </c>
       <c r="R5" t="n">
-        <v>7152830</v>
+        <v>7152983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753548</v>
+        <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>78010</v>
+        <v>91436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>743086</v>
+        <v>743160</v>
       </c>
       <c r="R6" t="n">
-        <v>7152983</v>
+        <v>7152830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753529</v>
+        <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92843</v>
+        <v>92746</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743161</v>
+        <v>743213</v>
       </c>
       <c r="R7" t="n">
-        <v>7152726</v>
+        <v>7152697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753523</v>
+        <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>92654</v>
+        <v>92935</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743213</v>
+        <v>743161</v>
       </c>
       <c r="R8" t="n">
-        <v>7152697</v>
+        <v>7152726</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753543</v>
+        <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>92650</v>
+        <v>92935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743147</v>
+        <v>743184</v>
       </c>
       <c r="R9" t="n">
-        <v>7152782</v>
+        <v>7152932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753526</v>
+        <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743184</v>
+        <v>743212</v>
       </c>
       <c r="R10" t="n">
-        <v>7152932</v>
+        <v>7152903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753527</v>
+        <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92843</v>
+        <v>92742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743212</v>
+        <v>743147</v>
       </c>
       <c r="R11" t="n">
-        <v>7152903</v>
+        <v>7152782</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127753520</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91521</v>
+        <v>91613</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92654</v>
+        <v>92746</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753530</v>
+        <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>92088</v>
+        <v>80217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1105</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>743176</v>
+        <v>743242</v>
       </c>
       <c r="R22" t="n">
-        <v>7152744</v>
+        <v>7152788</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,32 +2725,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753522</v>
+        <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>80164</v>
+        <v>92180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>1105</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>743242</v>
+        <v>743176</v>
       </c>
       <c r="R23" t="n">
-        <v>7152788</v>
+        <v>7152744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90393</v>
+        <v>90485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127753521</v>
+        <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>57833</v>
+        <v>91466</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3124,42 +3124,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>743184</v>
+        <v>743129</v>
       </c>
       <c r="R27" t="n">
-        <v>7152932</v>
+        <v>7152731</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3218,10 +3210,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753534</v>
+        <v>127753521</v>
       </c>
       <c r="B28" t="n">
-        <v>91374</v>
+        <v>57845</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3229,34 +3221,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743129</v>
+        <v>743184</v>
       </c>
       <c r="R28" t="n">
-        <v>7152731</v>
+        <v>7152932</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90393</v>
+        <v>90485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91621</v>
+        <v>91713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91466</v>
+        <v>91518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92935</v>
+        <v>92989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>78055</v>
+        <v>78092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1071,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91436</v>
+        <v>91488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,14 +1172,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92746</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,14 +1273,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>92935</v>
+        <v>92989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,14 +1374,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>92935</v>
+        <v>92989</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,14 +1475,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>92935</v>
+        <v>92989</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,14 +1576,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,14 +1677,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,14 +1778,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91417</v>
+        <v>91469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,14 +1879,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127753520</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,14 +1993,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91613</v>
+        <v>91665</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,14 +2094,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>78749</v>
+        <v>78786</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,14 +2195,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,14 +2296,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,14 +2397,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,14 +2498,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92746</v>
+        <v>92798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,14 +2599,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,14 +2700,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>80217</v>
+        <v>80254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,14 +2801,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92180</v>
+        <v>92232</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,14 +2902,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>92794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,14 +3003,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90485</v>
+        <v>90536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,14 +3104,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,14 +3205,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91466</v>
+        <v>91518</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,14 +3306,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>127753521</v>
       </c>
       <c r="B28" t="n">
-        <v>57845</v>
+        <v>57876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,14 +3415,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90485</v>
+        <v>90536</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3408,14 +3516,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91713</v>
+        <v>91765</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,7 +3617,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>78092</v>
+        <v>78096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91488</v>
+        <v>91492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127753520</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91665</v>
+        <v>91669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92232</v>
+        <v>92236</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>127753521</v>
       </c>
       <c r="B28" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91765</v>
+        <v>91769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>78096</v>
+        <v>78037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91492</v>
+        <v>91497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127753520</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91669</v>
+        <v>91674</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92236</v>
+        <v>92241</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>127753521</v>
       </c>
       <c r="B28" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91769</v>
+        <v>91774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91681</v>
+        <v>91684</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92249</v>
+        <v>92254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>78042</v>
+        <v>78043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91507</v>
+        <v>91510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91684</v>
+        <v>91687</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92254</v>
+        <v>92257</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91784</v>
+        <v>91787</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91510</v>
+        <v>91517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127753520</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91687</v>
+        <v>91694</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92257</v>
+        <v>92264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>127753521</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91787</v>
+        <v>91794</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91517</v>
+        <v>91524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91694</v>
+        <v>91701</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92264</v>
+        <v>92271</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91794</v>
+        <v>91801</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>78047</v>
+        <v>78049</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91524</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127753520</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92271</v>
+        <v>92273</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>127753521</v>
       </c>
       <c r="B28" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>91524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91703</v>
+        <v>91712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92273</v>
+        <v>92287</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91803</v>
+        <v>91812</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91712</v>
+        <v>91713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92287</v>
+        <v>92288</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>78049</v>
+        <v>78051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91524</v>
+        <v>91527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92288</v>
+        <v>92291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91813</v>
+        <v>91816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127753548</v>
       </c>
       <c r="B5" t="n">
-        <v>78051</v>
+        <v>78052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91527</v>
+        <v>91529</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127753536</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91716</v>
+        <v>91718</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>127753540</v>
       </c>
       <c r="B16" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>127753522</v>
       </c>
       <c r="B22" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92291</v>
+        <v>92293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>127753537</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91816</v>
+        <v>91818</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127753533</v>
       </c>
       <c r="B2" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127753528</v>
       </c>
       <c r="B3" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127753544</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127753525</v>
       </c>
       <c r="B6" t="n">
-        <v>91529</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127753523</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127753529</v>
       </c>
       <c r="B8" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127753526</v>
       </c>
       <c r="B9" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127753527</v>
       </c>
       <c r="B10" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127753543</v>
       </c>
       <c r="B11" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127753516</v>
       </c>
       <c r="B13" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91718</v>
+        <v>91722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>127753547</v>
       </c>
       <c r="B17" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>127753542</v>
       </c>
       <c r="B18" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>127753541</v>
       </c>
       <c r="B19" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>127753524</v>
       </c>
       <c r="B20" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127753546</v>
       </c>
       <c r="B21" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>127753530</v>
       </c>
       <c r="B23" t="n">
-        <v>92293</v>
+        <v>92297</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>127753545</v>
       </c>
       <c r="B24" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>127753518</v>
       </c>
       <c r="B25" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>127753534</v>
       </c>
       <c r="B27" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>127753517</v>
       </c>
       <c r="B29" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>127753539</v>
       </c>
       <c r="B30" t="n">
-        <v>91818</v>
+        <v>91822</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91722</v>
+        <v>91957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91982</v>
+        <v>91983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -2004,7 +2004,7 @@
         <v>127753535</v>
       </c>
       <c r="B15" t="n">
-        <v>91983</v>
+        <v>91986</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3620,6 +3620,1016 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131739270</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79850</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nymyran Nord, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>743205</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7152925</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131739450</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90851</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Innanheden Syd, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>743211</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7152697</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131732508</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78926</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>353</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Innanheden Syd, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>743172</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7152736</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131737476</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nymyran Nord, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>743169</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7152952</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131734650</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79017</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nymyran Nord, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>743169</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7152956</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131737589</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93154</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Innanheden Sydväst, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>743156</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7152867</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131738965</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nymyran Nord, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>743169</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7152955</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131738957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nymyran Nord, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>743203</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7152928</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131732509</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78926</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>353</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nymyran Nord, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>743156</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7152970</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131737372</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Innanheden Syd, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>743167</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7152728</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -3628,7 +3628,7 @@
         <v>131739270</v>
       </c>
       <c r="B31" t="n">
-        <v>79850</v>
+        <v>79851</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>131739450</v>
       </c>
       <c r="B32" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131732508</v>
+        <v>131737476</v>
       </c>
       <c r="B33" t="n">
-        <v>78926</v>
+        <v>79019</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3838,34 +3838,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Innanheden Syd, Vb</t>
+          <t>Nymyran Nord, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>743172</v>
+        <v>743169</v>
       </c>
       <c r="R33" t="n">
-        <v>7152736</v>
+        <v>7152952</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737476</v>
+        <v>131732508</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>78927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,34 +3939,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nymyran Nord, Vb</t>
+          <t>Innanheden Syd, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>743169</v>
+        <v>743172</v>
       </c>
       <c r="R34" t="n">
-        <v>7152952</v>
+        <v>7152736</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4032,7 +4032,7 @@
         <v>131734650</v>
       </c>
       <c r="B35" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>131737589</v>
       </c>
       <c r="B36" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>131738965</v>
       </c>
       <c r="B37" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>131738957</v>
       </c>
       <c r="B38" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>131732509</v>
       </c>
       <c r="B39" t="n">
-        <v>78926</v>
+        <v>78927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>131737372</v>
       </c>
       <c r="B40" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -3628,7 +3628,7 @@
         <v>131739270</v>
       </c>
       <c r="B31" t="n">
-        <v>79851</v>
+        <v>79854</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>131739450</v>
       </c>
       <c r="B32" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737476</v>
+        <v>131732508</v>
       </c>
       <c r="B33" t="n">
-        <v>79019</v>
+        <v>78930</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3838,34 +3838,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nymyran Nord, Vb</t>
+          <t>Innanheden Syd, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>743169</v>
+        <v>743172</v>
       </c>
       <c r="R33" t="n">
-        <v>7152952</v>
+        <v>7152736</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131732508</v>
+        <v>131737476</v>
       </c>
       <c r="B34" t="n">
-        <v>78927</v>
+        <v>79022</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,34 +3939,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Innanheden Syd, Vb</t>
+          <t>Nymyran Nord, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>743172</v>
+        <v>743169</v>
       </c>
       <c r="R34" t="n">
-        <v>7152736</v>
+        <v>7152952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4032,7 +4032,7 @@
         <v>131734650</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>131737589</v>
       </c>
       <c r="B36" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>131738965</v>
       </c>
       <c r="B37" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>131738957</v>
       </c>
       <c r="B38" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>131732509</v>
       </c>
       <c r="B39" t="n">
-        <v>78927</v>
+        <v>78930</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>131737372</v>
       </c>
       <c r="B40" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -3827,10 +3827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131732508</v>
+        <v>131737476</v>
       </c>
       <c r="B33" t="n">
-        <v>78930</v>
+        <v>79022</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3838,34 +3838,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Innanheden Syd, Vb</t>
+          <t>Nymyran Nord, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>743172</v>
+        <v>743169</v>
       </c>
       <c r="R33" t="n">
-        <v>7152736</v>
+        <v>7152952</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737476</v>
+        <v>131732508</v>
       </c>
       <c r="B34" t="n">
-        <v>79022</v>
+        <v>78930</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,34 +3939,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nymyran Nord, Vb</t>
+          <t>Innanheden Syd, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>743169</v>
+        <v>743172</v>
       </c>
       <c r="R34" t="n">
-        <v>7152952</v>
+        <v>7152736</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -3827,10 +3827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737476</v>
+        <v>131732508</v>
       </c>
       <c r="B33" t="n">
-        <v>79022</v>
+        <v>78930</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3838,34 +3838,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nymyran Nord, Vb</t>
+          <t>Innanheden Syd, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>743169</v>
+        <v>743172</v>
       </c>
       <c r="R33" t="n">
-        <v>7152952</v>
+        <v>7152736</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131732508</v>
+        <v>131737476</v>
       </c>
       <c r="B34" t="n">
-        <v>78930</v>
+        <v>79022</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,34 +3939,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Innanheden Syd, Vb</t>
+          <t>Nymyran Nord, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>743172</v>
+        <v>743169</v>
       </c>
       <c r="R34" t="n">
-        <v>7152736</v>
+        <v>7152952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -3628,7 +3628,7 @@
         <v>131739270</v>
       </c>
       <c r="B31" t="n">
-        <v>79854</v>
+        <v>79856</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>131739450</v>
       </c>
       <c r="B32" t="n">
-        <v>90855</v>
+        <v>90861</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>131732508</v>
       </c>
       <c r="B33" t="n">
-        <v>78930</v>
+        <v>78932</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>131737476</v>
       </c>
       <c r="B34" t="n">
-        <v>79022</v>
+        <v>79024</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>131734650</v>
       </c>
       <c r="B35" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>131737589</v>
       </c>
       <c r="B36" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>131738965</v>
       </c>
       <c r="B37" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>131738957</v>
       </c>
       <c r="B38" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>131732509</v>
       </c>
       <c r="B39" t="n">
-        <v>78930</v>
+        <v>78932</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>131737372</v>
       </c>
       <c r="B40" t="n">
-        <v>91885</v>
+        <v>91891</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -3628,7 +3628,7 @@
         <v>131739270</v>
       </c>
       <c r="B31" t="n">
-        <v>79905</v>
+        <v>79907</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>131739450</v>
       </c>
       <c r="B32" t="n">
-        <v>90912</v>
+        <v>90915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>131732508</v>
       </c>
       <c r="B33" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>131737476</v>
       </c>
       <c r="B34" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>131734650</v>
       </c>
       <c r="B35" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>131737589</v>
       </c>
       <c r="B36" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>131738965</v>
       </c>
       <c r="B37" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>131738957</v>
       </c>
       <c r="B38" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>131732509</v>
       </c>
       <c r="B39" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>131737372</v>
       </c>
       <c r="B40" t="n">
-        <v>91942</v>
+        <v>91945</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127753533</v>
+        <v>127753539</v>
       </c>
       <c r="B2" t="n">
-        <v>91563</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743182</v>
+        <v>743171</v>
       </c>
       <c r="R2" t="n">
-        <v>7152845</v>
+        <v>7152962</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127753528</v>
+        <v>127753540</v>
       </c>
       <c r="B3" t="n">
-        <v>91602</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743133</v>
+        <v>743256</v>
       </c>
       <c r="R3" t="n">
-        <v>7152823</v>
+        <v>7152743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,45 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127753544</v>
+        <v>131732508</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nymyran, Vb</t>
+          <t>Innanheden Syd, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743130</v>
+        <v>743172</v>
       </c>
       <c r="R4" t="n">
-        <v>7152722</v>
+        <v>7152736</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,26 +962,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127753548</v>
+        <v>131732509</v>
       </c>
       <c r="B5" t="n">
-        <v>78052</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nymyran, Vb</t>
+          <t>Nymyran Nord, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743086</v>
+        <v>743156</v>
       </c>
       <c r="R5" t="n">
-        <v>7152983</v>
+        <v>7152970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,48 +1063,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127753525</v>
+        <v>127753530</v>
       </c>
       <c r="B6" t="n">
-        <v>91533</v>
+        <v>92662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>1105</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>743160</v>
+        <v>743176</v>
       </c>
       <c r="R6" t="n">
-        <v>7152830</v>
+        <v>7152744</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127753523</v>
+        <v>127753533</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>743213</v>
+        <v>743182</v>
       </c>
       <c r="R7" t="n">
-        <v>7152697</v>
+        <v>7152845</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127753529</v>
+        <v>127753534</v>
       </c>
       <c r="B8" t="n">
-        <v>91602</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>743161</v>
+        <v>743129</v>
       </c>
       <c r="R8" t="n">
-        <v>7152726</v>
+        <v>7152731</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127753526</v>
+        <v>127753535</v>
       </c>
       <c r="B9" t="n">
-        <v>91602</v>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743184</v>
+        <v>743161</v>
       </c>
       <c r="R9" t="n">
-        <v>7152932</v>
+        <v>7152726</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127753527</v>
+        <v>127753517</v>
       </c>
       <c r="B10" t="n">
-        <v>91602</v>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743212</v>
+        <v>743167</v>
       </c>
       <c r="R10" t="n">
-        <v>7152903</v>
+        <v>7152964</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127753543</v>
+        <v>127753518</v>
       </c>
       <c r="B11" t="n">
-        <v>92831</v>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743147</v>
+        <v>743133</v>
       </c>
       <c r="R11" t="n">
-        <v>7152782</v>
+        <v>7152823</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127753536</v>
+        <v>131739450</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>90997</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,34 +1696,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nymyran, Vb</t>
+          <t>Innanheden Syd, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743258</v>
+        <v>743211</v>
       </c>
       <c r="R12" t="n">
-        <v>7152769</v>
+        <v>7152697</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,48 +1770,48 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127753516</v>
+        <v>127753526</v>
       </c>
       <c r="B13" t="n">
-        <v>91513</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743257</v>
+        <v>743184</v>
       </c>
       <c r="R13" t="n">
-        <v>7152745</v>
+        <v>7152932</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127753520</v>
+        <v>127753527</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,42 +1898,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>743258</v>
+        <v>743212</v>
       </c>
       <c r="R14" t="n">
-        <v>7152769</v>
+        <v>7152903</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,11 +1958,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,32 +1988,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127753535</v>
+        <v>127753528</v>
       </c>
       <c r="B15" t="n">
-        <v>91986</v>
+        <v>91962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>743161</v>
+        <v>743133</v>
       </c>
       <c r="R15" t="n">
-        <v>7152726</v>
+        <v>7152823</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127753540</v>
+        <v>127753529</v>
       </c>
       <c r="B16" t="n">
-        <v>78710</v>
+        <v>91962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743256</v>
+        <v>743161</v>
       </c>
       <c r="R16" t="n">
-        <v>7152743</v>
+        <v>7152726</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,45 +2190,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127753547</v>
+        <v>131737372</v>
       </c>
       <c r="B17" t="n">
-        <v>92831</v>
+        <v>92027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nymyran, Vb</t>
+          <t>Innanheden Syd, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>743197</v>
+        <v>743167</v>
       </c>
       <c r="R17" t="n">
-        <v>7152675</v>
+        <v>7152728</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,12 +2255,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2288,30 +2275,30 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127753542</v>
+        <v>127753541</v>
       </c>
       <c r="B18" t="n">
-        <v>92831</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2339,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>743197</v>
+        <v>743108</v>
       </c>
       <c r="R18" t="n">
-        <v>7152921</v>
+        <v>7152950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2405,14 +2392,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127753541</v>
+        <v>127753542</v>
       </c>
       <c r="B19" t="n">
-        <v>92831</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2440,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>743108</v>
+        <v>743197</v>
       </c>
       <c r="R19" t="n">
-        <v>7152950</v>
+        <v>7152921</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,32 +2493,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127753524</v>
+        <v>127753543</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2541,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>743202</v>
+        <v>743147</v>
       </c>
       <c r="R20" t="n">
-        <v>7152703</v>
+        <v>7152782</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2607,14 +2594,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127753546</v>
+        <v>127753544</v>
       </c>
       <c r="B21" t="n">
-        <v>92831</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2642,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>743253</v>
+        <v>743130</v>
       </c>
       <c r="R21" t="n">
-        <v>7152732</v>
+        <v>7152722</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,32 +2695,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127753522</v>
+        <v>127753545</v>
       </c>
       <c r="B22" t="n">
-        <v>80178</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2743,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>743242</v>
+        <v>743174</v>
       </c>
       <c r="R22" t="n">
-        <v>7152788</v>
+        <v>7152721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2809,32 +2796,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127753530</v>
+        <v>127753546</v>
       </c>
       <c r="B23" t="n">
-        <v>92297</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1105</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2844,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>743176</v>
+        <v>743253</v>
       </c>
       <c r="R23" t="n">
-        <v>7152744</v>
+        <v>7152732</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2910,14 +2897,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127753545</v>
+        <v>127753547</v>
       </c>
       <c r="B24" t="n">
-        <v>92831</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2945,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>743174</v>
+        <v>743197</v>
       </c>
       <c r="R24" t="n">
-        <v>7152721</v>
+        <v>7152675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3011,32 +2998,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127753518</v>
+        <v>127753523</v>
       </c>
       <c r="B25" t="n">
-        <v>90581</v>
+        <v>93201</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3046,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743133</v>
+        <v>743213</v>
       </c>
       <c r="R25" t="n">
-        <v>7152823</v>
+        <v>7152697</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3112,32 +3099,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127753537</v>
+        <v>127753524</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>93201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3147,10 +3134,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743060</v>
+        <v>743202</v>
       </c>
       <c r="R26" t="n">
-        <v>7152820</v>
+        <v>7152703</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3213,32 +3200,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127753534</v>
+        <v>127753525</v>
       </c>
       <c r="B27" t="n">
-        <v>91563</v>
+        <v>91893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>4660</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3248,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>743129</v>
+        <v>743160</v>
       </c>
       <c r="R27" t="n">
-        <v>7152731</v>
+        <v>7152830</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,53 +3301,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127753521</v>
+        <v>127753516</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743184</v>
+        <v>743257</v>
       </c>
       <c r="R28" t="n">
-        <v>7152932</v>
+        <v>7152745</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127753517</v>
+        <v>131737589</v>
       </c>
       <c r="B29" t="n">
-        <v>90581</v>
+        <v>93309</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3434,34 +3413,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nymyran, Vb</t>
+          <t>Innanheden Sydväst, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>743167</v>
+        <v>743156</v>
       </c>
       <c r="R29" t="n">
-        <v>7152964</v>
+        <v>7152867</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,12 +3467,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3508,26 +3487,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127753539</v>
+        <v>127753536</v>
       </c>
       <c r="B30" t="n">
-        <v>91822</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3535,21 +3514,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3559,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>743171</v>
+        <v>743258</v>
       </c>
       <c r="R30" t="n">
-        <v>7152962</v>
+        <v>7152769</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,45 +3604,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131739270</v>
+        <v>127753537</v>
       </c>
       <c r="B31" t="n">
-        <v>79907</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nymyran Nord, Vb</t>
+          <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>743205</v>
+        <v>743060</v>
       </c>
       <c r="R31" t="n">
-        <v>7152925</v>
+        <v>7152820</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,12 +3669,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3710,26 +3689,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131739450</v>
+        <v>131734650</v>
       </c>
       <c r="B32" t="n">
-        <v>90915</v>
+        <v>79130</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,34 +3716,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Innanheden Syd, Vb</t>
+          <t>Nymyran Nord, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>743211</v>
+        <v>743169</v>
       </c>
       <c r="R32" t="n">
-        <v>7152697</v>
+        <v>7152956</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3827,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131732508</v>
+        <v>131738957</v>
       </c>
       <c r="B33" t="n">
-        <v>78983</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3838,34 +3817,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Innanheden Syd, Vb</t>
+          <t>Nymyran Nord, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>743172</v>
+        <v>743203</v>
       </c>
       <c r="R33" t="n">
-        <v>7152736</v>
+        <v>7152928</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,10 +3907,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737476</v>
+        <v>131738965</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,21 +3918,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3966,7 +3945,7 @@
         <v>743169</v>
       </c>
       <c r="R34" t="n">
-        <v>7152952</v>
+        <v>7152955</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4029,45 +4008,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131734650</v>
+        <v>127753522</v>
       </c>
       <c r="B35" t="n">
-        <v>79074</v>
+        <v>80461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nymyran Nord, Vb</t>
+          <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>743169</v>
+        <v>743242</v>
       </c>
       <c r="R35" t="n">
-        <v>7152956</v>
+        <v>7152788</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4094,12 +4073,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4114,26 +4093,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131737589</v>
+        <v>127753548</v>
       </c>
       <c r="B36" t="n">
-        <v>93218</v>
+        <v>78334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4141,34 +4120,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Innanheden Sydväst, Vb</t>
+          <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>743156</v>
+        <v>743086</v>
       </c>
       <c r="R36" t="n">
-        <v>7152867</v>
+        <v>7152983</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4195,12 +4174,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4215,26 +4194,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131738965</v>
+        <v>127753520</v>
       </c>
       <c r="B37" t="n">
-        <v>79936</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4242,34 +4221,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nymyran Nord, Vb</t>
+          <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>743169</v>
+        <v>743258</v>
       </c>
       <c r="R37" t="n">
-        <v>7152955</v>
+        <v>7152769</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,12 +4283,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4316,26 +4308,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131738957</v>
+        <v>127753521</v>
       </c>
       <c r="B38" t="n">
-        <v>79936</v>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4343,34 +4335,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nymyran Nord, Vb</t>
+          <t>Nymyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>743203</v>
+        <v>743184</v>
       </c>
       <c r="R38" t="n">
-        <v>7152928</v>
+        <v>7152932</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4417,26 +4417,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131732509</v>
+        <v>131737476</v>
       </c>
       <c r="B39" t="n">
-        <v>78983</v>
+        <v>79131</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4444,21 +4444,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>743156</v>
+        <v>743169</v>
       </c>
       <c r="R39" t="n">
-        <v>7152970</v>
+        <v>7152952</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131737372</v>
+        <v>131739270</v>
       </c>
       <c r="B40" t="n">
-        <v>91945</v>
+        <v>79963</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4545,34 +4545,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Innanheden Syd, Vb</t>
+          <t>Nymyran Nord, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>743167</v>
+        <v>743205</v>
       </c>
       <c r="R40" t="n">
-        <v>7152728</v>
+        <v>7152925</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 35969-2025 artfynd.xlsx
+++ b/artfynd/A 35969-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753539</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753540</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732508</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732509</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753530</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753533</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753534</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753535</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753517</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753518</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739450</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753526</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753527</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753528</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753529</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737372</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753541</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753542</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753543</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753544</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753545</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753546</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753547</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753523</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753524</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753525</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753516</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737589</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3601,6 +3746,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753536</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3702,6 +3852,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753537</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3803,6 +3958,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734650</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3904,6 +4064,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738957</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4005,6 +4170,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738965</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4106,6 +4276,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753522</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4207,6 +4382,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753548</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4321,6 +4501,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753520</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4430,6 +4615,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127753521</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4531,6 +4721,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737476</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4632,8 +4827,54 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739270</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>